--- a/data/new_products.xlsx
+++ b/data/new_products.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр + 2 оригинальных пыльника + 2 оригинальных сальника VAG DSG7 DQ200, полный комплект</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/data/new_products.xlsx
+++ b/data/new_products.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -459,60 +459,65 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Образец ТОЛЬКО для WB, если Ozon-образец на WB не продаётся (необязательно — пусто = взять тот же, что для Ozon)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Название (для WB автоматически обрежется до 60 символов)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Описание</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Цена, ₽</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Цена до скидки, ₽ (необязательно, только Ozon)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Код ТН ВЭД — обязательно для Ozon (иначе карточка останется черновиком)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Вес, г (пусто = как у образца)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Длина, мм (пусто = как у образца)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Ширина, мм (пусто = как у образца)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Высота, мм (пусто = как у образца)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Кол-во к продаже (остаток)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Заметки</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Хэштеги / ключевые слова через запятую (необязательно, только Ozon)</t>
         </is>
@@ -531,36 +536,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0am3250066AE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>7500</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>12000</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>8708409909</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>ЧЕРНОВИК: проверьте цену/фото перед push-new-product-all</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>плита фильтр dsg7 dq200 ремкомплект мехатроника</t>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>#плита #фильтр #dsg7 #dq200 #ремкомплект #мехатроник</t>
         </is>
       </c>
     </row>
@@ -577,36 +587,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0am3250066AE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>9500</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>13500</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>8708409909</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>ЧЕРНОВИК: проверьте цену/фото перед push-new-product-all</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>плита фильтр пыльники сальники оригинал dsg7 dq200 ремкомплект</t>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>#плита #фильтр #пыльники #сальники #оригинал #dsg7 #dq200 #ремкомплект</t>
         </is>
       </c>
     </row>
@@ -623,36 +638,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0am3250066AE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>8500</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>13000</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>8708409909</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>ЧЕРНОВИК: проверьте цену/фото перед push-new-product-all</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>плита пыльники сальники dsg7 dq200 ремкомплект мехатроника</t>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>#плита #пыльники #сальники #dsg7 #dq200 #ремкомплект #мехатроник</t>
         </is>
       </c>
     </row>

--- a/data/new_products.xlsx
+++ b/data/new_products.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Новый товар — все площадки" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новый товар — все площадки'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Новый товар — все площадки'!$A$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,23 +427,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,38 +527,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0am3250066AE</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW — фильтр гидроблока управления АКПП (сухой робот 0AM/0CW). 🔧 Применяется при ремонте и плановой замене масла мехатроника DSG7 DQ200 на автомобилях Volkswagen, Audi, Škoda, Seat — подходит на все модификации DQ200. ✅ Новый, с завода. 📦 Всегда в наличии, отправка в день заказа. 🔩 Совместим с 0AM/0CW DSG7 DQ200.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7500</v>
+        <v>990</v>
       </c>
       <c r="G2" t="n">
-        <v>12000</v>
+        <v>1300</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8708409909</t>
+          <t>8708405001</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -565,119 +561,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ЧЕРНОВИК: проверьте цену/фото перед push-new-product-all</t>
+          <t>ЧЕРНОВИК: проверьте цену; остаток (0) замените на реальное количество этого фильтра на складе перед push-stock</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>#плита #фильтр #dsg7 #dq200 #ремкомплект #мехатроник</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-sal</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0am3250066AE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G3" t="n">
-        <v>13500</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>8708409909</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ЧЕРНОВИК: проверьте цену/фото перед push-new-product-all</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>#плита #фильтр #пыльники #сальники #оригинал #dsg7 #dq200 #ремкомплект</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0am3250066AE</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>8500</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13000</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>8708409909</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>ЧЕРНОВИК: проверьте цену/фото перед push-new-product-all</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>#плита #пыльники #сальники #dsg7 #dq200 #ремкомплект #мехатроник</t>
+          <t>#масляный #фильтр #мехатроник #гидроблок #dsg7 #dq200 #0am #0cw</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/new_products.xlsx
+++ b/data/new_products.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -527,46 +527,466 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>filtr-dsg7-dq500</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0AM325433E</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>🔧 Масляный фильтр мехатроника DSG7 DQ500 0BH325183B — устанавливается в корпус фильтра (корпус — отдельная позиция, см. также в нашем магазине). ✅ Volkswagen Passat, Golf, Tiguan, T5/T6, Audi A3, Škoda Kodiaq и другие модели с DSG7 DQ500/DQ400E. 📦 Новый, с завода, в наличии, отправка в день заказа. 🔩 Артикул: 0BH325183B.</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1290</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8708405001</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>65</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ЧЕРНОВИК: проверьте цену. Остаток заполнен пользователем: 65 шт.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>#масляный #фильтр #мехатроник #dsg7 #dq500 #0bh325183b</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>separatornaya-plastina-dq200</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0AM325467J</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>🔧 Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;📦 Новая, с завода, отправка в день заказа.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>490</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>75</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>#сепараторная #пластина #мехатроник #dsg7 #dq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>plastina-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0AM325467J</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>🔧 Пластина (фиксатор) на соленоиды мехатроника DSG7 DQ200, 1 шт.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;📦 Новая, с завода, отправка в день заказа.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>490</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>#пластина #соленоид #мехатроник #dsg7 #dq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-dq200-2sht</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0AM325467J</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Пластины на соленоиды мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>🔧 Пластины (фиксаторы) на соленоиды мехатроника DSG7 DQ200 — комплект 2 шт на весь мехатроник.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;📦 Новые, с завода.</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>980</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Остаток считается автоматически из plastina-solenoid-dq200 x2 через kits.xlsx/recompute-kit-stock — сюда 0, руками не трогать.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>#пластины #соленоид #мехатроник #dsg7 #dq200 #комплект</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0AM325467J</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>🔧 Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.&lt;br/&gt;&lt;br/&gt;📦 Новые, с завода.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1870</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Остаток считается автоматически из separatornaya-plastina-dq200 x1 + plastina-solenoid-dq200 x2 через kits.xlsx/recompute-kit-stock — сюда 0, руками не трогать.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>#комплект #сепараторная #пластины #соленоид #мехатроник #dsg7 #dq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>filtr-dsg7-dq200</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>0AM325433E</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW — фильтр гидроблока управления АКПП (сухой робот 0AM/0CW). 🔧 Применяется при ремонте и плановой замене масла мехатроника DSG7 DQ200 на автомобилях Volkswagen, Audi, Škoda, Seat — подходит на все модификации DQ200. ✅ Новый, с завода. 📦 Всегда в наличии, отправка в день заказа. 🔩 Совместим с 0AM/0CW DSG7 DQ200.</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>990</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1300</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>🔧 Масляный фильтр мехатроника DSG7 DQ200 (0AM/0CW) — стандартная версия для планового обслуживания и ремонта гидроблока АКПП.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200 (0AM325025 и аналоги).&lt;br/&gt;&lt;br/&gt;📦 Новый, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;⭐ Нужен максимальный ресурс? У нас есть улучшенная версия фильтра — смотрите в нашем магазине.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: filtr-dsg7-dq200.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>980</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>8708405001</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ЧЕРНОВИК: проверьте цену; остаток (0) замените на реальное количество этого фильтра на складе перед push-stock</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>#масляный #фильтр #мехатроник #гидроблок #dsg7 #dq200 #0am #0cw</t>
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ЧЕРНОВИК: проверьте текст/фото перед push. Цена Ozon/WB = 980₽ (по формуле пользователя). Цена Avito/сайт = 490₽ — ровно половина, авто-оверрайд не нужен (пересчитается автоматически при push-new-product-all).</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>#фильтр_мехатроника_dq200,#масляный_фильтр_dsg7,#фильтр_гидроблока_акпп,#dq200,#dsg7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>kryshka-mehatronika-dq200</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0AM325219C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>🔧 Крышка (поддон) мехатроника DSG7 DQ200 — герметично закрывает гидроблок, защищает от загрязнений и подтёков масла.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новая, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Совместима с 0AM325219C.</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1950</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8708405001</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ЧЕРНОВИК: проверьте текст/фото перед push. Название разграничено с 0AM325219C: у оригинала в wb_catalog.xlsx название теперь тоже "Оригинальная крышка..." (было без этого слова, поправил для единообразия с Ozon), у этого черновика название осталось без слова "оригинальная" — коллизии больше нет. Цена Ozon/WB = 1950₽, Avito/сайт = 1250₽ (задано вручную, оверрайд в data/avito_site_price_overrides.xlsx).</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>#крышка_мехатроника_dq200,#поддон_мехатроника,#dq200,#dsg7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>solenoid-02e-0b5-bolshoy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0AM325025B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500, большой</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>🔧 Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.&lt;br/&gt;&lt;br/&gt;🔄 Восстановлен: проверен и протестирован перед отправкой.&lt;br/&gt;&lt;br/&gt;📦 В наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: solenoid-02e-0b5-bolshoy.</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5700</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ЧЕРНОВИК: проверьте текст/фото перед push. Цена Ozon/WB = 5700₽, Avito/сайт = 2850₽ (задано пользователем, ×2 — ровно половина, авто-оверрайд не нужен).</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>#соленоид_dq250,#соленоид_dq500,#соленоид_0b5,#dl501,#мехатроник_02e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0AM325443D</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>🔧 Прокладка крышки (поддона) мехатроника DSG7 DQ200 — герметизирует соединение крышки с корпусом, предотвращает подтёки масла.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новая, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;⭐ Нужен увеличенный ресурс? У нас есть усиленная (утолщённая) версия прокладки — смотрите в нашем магазине.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-kryshki-dq200.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>ЧЕРНОВИК: проверьте текст/фото перед push. Цена Ozon/WB = 1380₽, Avito/сайт = 690₽ (ровно половина, авто-оверрайд не нужен). Не путать с усиленной (0AM325443D, 73 шт) — эта версия обычная, без усиления.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>#прокладка_крышки_dq200,#прокладка_поддона_dq200,#dq200,#dsg7,#мехатроник</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>prokladka-vtulki-verh-dq200</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0am325025D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>🔧 Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>580</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>49</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>ЧЕРНОВИК: проверьте текст/фото перед push. Цена Ozon/WB = 580₽, Avito/сайт = 290₽ (ровно половина, авто-оверрайд не нужен).</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>#кольцо_втулки_dq200,#прокладка_втулки,#dq200,#dsg7,#мехатроник</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>prokladka-vtulki-niz-dq200</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0am325025D</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>🔧 Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>580</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>8708409909</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>49</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>ЧЕРНОВИК: проверьте текст/фото перед push. Цена Ozon/WB = 580₽, Avito/сайт = 290₽ (ровно половина, авто-оверрайд не нужен).</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>#кольцо_втулки_dq200,#прокладка_втулки,#dq200,#dsg7,#мехатроник</t>
         </is>
       </c>
     </row>

--- a/data/new_products.xlsx
+++ b/data/new_products.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>#фильтр_мехатроника_dq200,#масляный_фильтр_dsg7,#фильтр_гидроблока_акпп,#dq200,#dsg7</t>
+          <t>#фильтр_мехатроника_dq200 #масляный_фильтр_dsg7 #фильтр_гидроблока_акпп #dq200 #dsg7</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>#крышка_мехатроника_dq200,#поддон_мехатроника,#dq200,#dsg7</t>
+          <t>#крышка_мехатроника_dq200 #поддон_мехатроника #dq200 #dsg7</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>#соленоид_dq250,#соленоид_dq500,#соленоид_0b5,#dl501,#мехатроник_02e</t>
+          <t>#соленоид_dq250 #соленоид_dq500 #соленоид_0b5 #dl501 #мехатроник_02e</t>
         </is>
       </c>
     </row>
@@ -900,14 +900,14 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>#прокладка_крышки_dq200,#прокладка_поддона_dq200,#dq200,#dsg7,#мехатроник</t>
+          <t>#прокладка_крышки_dq200 #прокладка_поддона_dq200 #dq200 #dsg7 #мехатроник</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -917,16 +917,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
+          <t>2 кольца-прокладки на 1 втулку мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>🔧 Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
+          <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0am325091F и длинные 101мм 0AM325091E.&lt;br/&gt;&lt;br/&gt;✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новые, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-dq200.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>580</v>
+        <v>840</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -938,55 +938,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ЧЕРНОВИК: проверьте текст/фото перед push. Цена Ozon/WB = 580₽, Avito/сайт = 290₽ (ровно половина, авто-оверрайд не нужен).</t>
+          <t>ЧЕРНОВИК: проверьте текст/фото перед push. Объединено из verh+niz в один товар (2 шт комплект), 2026-09-24. Цена Ozon/WB = 840₽, Avito/сайт = 420₽ (ровно половина, авто-оверрайд не нужен).</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>#кольцо_втулки_dq200,#прокладка_втулки,#dq200,#dsg7,#мехатроник</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>prokladka-vtulki-niz-dq200</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0am325025D</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>🔧 Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.&lt;br/&gt;&lt;br/&gt;✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.&lt;br/&gt;&lt;br/&gt;📦 Новое, в наличии, отправка в день заказа.&lt;br/&gt;&lt;br/&gt;🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>580</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>8708409909</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>49</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>ЧЕРНОВИК: проверьте текст/фото перед push. Цена Ozon/WB = 580₽, Avito/сайт = 290₽ (ровно половина, авто-оверрайд не нужен).</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>#кольцо_втулки_dq200,#прокладка_втулки,#dq200,#dsg7,#мехатроник</t>
+          <t>#кольцо_втулки_dq200 #прокладка_втулки #dq200 #dsg7 #мехатроник</t>
         </is>
       </c>
     </row>
